--- a/public/Template_Master_Data_KosanKu_Pro.xlsx
+++ b/public/Template_Master_Data_KosanKu_Pro.xlsx
@@ -3,11 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="01_Identitas_Kosan" sheetId="1" r:id="rId1"/>
-    <sheet name="02_Master_Kamar" sheetId="2" r:id="rId2"/>
-    <sheet name="03_Penghuni_Aktif" sheetId="3" r:id="rId3"/>
-    <sheet name="04_Checklist_CekIn" sheetId="4" r:id="rId4"/>
-    <sheet name="05_Karyawan_Vendor" sheetId="5" r:id="rId5"/>
+    <sheet name="00_Panduan_Konsultasi" sheetId="1" r:id="rId1"/>
+    <sheet name="01_Identitas_Kosan" sheetId="2" r:id="rId2"/>
+    <sheet name="02_Master_Kamar" sheetId="3" r:id="rId3"/>
+    <sheet name="03_Data_Penghuni" sheetId="4" r:id="rId4"/>
+    <sheet name="04_Staf_Vendor" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -401,686 +401,936 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
+  <cols>
+    <col min="1" max="1" width="35.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>PARAMETER / FIELD PENGATURAN</v>
-      </c>
-      <c r="B1" t="str">
-        <v>NILAI / ISIAN OWNER</v>
-      </c>
-      <c r="C1" t="str">
-        <v>PETUNJUK &amp; KETERANGAN</v>
+        <v>=== FORM ONBOARDING &amp; SETUP MASTER DATA KOSANKU PRO ===</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Nama Properti / Kosan</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Kosan RSHS Pasteur Bandung</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Wajib diisi - Ditampilkan di header web &amp; invoice</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Tagline / Slogan Kosan</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Hunian Nyaman, Tenang &amp; Strategis Dekat RSHS Bandung</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Opsional - Tampil di halaman depan</v>
+        <v>ANDA PUNYA KOSAN TAPI BELUM PUNYA SISTEM DIGITAL OTOMATIS?</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Alamat Lengkap</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Jl. Pasteur No. 38, Sukajadi</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Wajib diisi</v>
+        <v>Daftar sekarang atau Konsultasi Gratis bersama Tim Konsultan KosanKu Pro:</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Kota / Wilayah</v>
+        <v>WhatsApp Hotline:</v>
       </c>
       <c r="B5" t="str">
-        <v>Bandung</v>
+        <v>+6282114242634</v>
       </c>
       <c r="C5" t="str">
-        <v>Wajib diisi</v>
+        <v>https://wa.me/6282114242634?text=Halo%20Admin%20KosanKu%20Pro,%20saya%20tertarik%20setup%20sistem%20kos%20saya</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>No. WhatsApp Resmi Kosan</v>
+        <v>Website:</v>
       </c>
       <c r="B6" t="str">
-        <v>081234567890</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Wajib diisi - Digunakan untuk notifikasi &amp; komplain</v>
+        <v>https://kosankupro.cloud</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Email Resmi Pengelola</v>
-      </c>
-      <c r="B7" t="str">
-        <v>admin.rshs@kosanku.pro</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Opsional</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Link Google Maps</v>
-      </c>
-      <c r="B8" t="str">
-        <v>https://maps.google.com/?q=-6.897368,107.598642</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Opsional - Link titik lokasi kos</v>
+        <v>--- PETUNJUK PENGISIAN FORMULIR (UNTUK OWNER / PENGELOLA) ---</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nama Bank Rekening Pencairan</v>
-      </c>
-      <c r="B9" t="str">
-        <v>BCA (Bank Central Asia)</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Wajib diisi - Rekening penerimaan uang sewa</v>
+        <v>1. Sheet 01_Identitas_Kosan: Isi data nama kosan, alamat, kontak resmi WhatsApp kosan, dan nomor rekening penerimaan uang sewa.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Nomor Rekening Bank</v>
-      </c>
-      <c r="B10" t="str">
-        <v>8830192844</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Wajib diisi</v>
+        <v>2. Sheet 02_Master_Kamar: Isi daftar unit kamar, nomor kamar, lantai, tipe kamar, tarif bulanan, dan fasilitas bawaan kamar.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Nama Pemilik Rekening (Holder)</v>
-      </c>
-      <c r="B11" t="str">
-        <v>PT KosanKu Pro Indonesia / dr. H. Subagyo</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Wajib diisi</v>
+        <v>3. Sheet 03_Data_Penghuni: Isi data penghuni yang saat ini aktif berjalan (opsional jika kamar masih kosong).</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Batas Tanggal Jatuh Tempo Tagihan</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Tanggal 1 - 5 setiap bulan</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Default tanggal penagihan invoice otomatis</v>
+        <v>4. Sheet 04_Staf_Vendor: Isi daftar penjaga kos / staf maintenance dan toko langganan (galon, laundry, gas) jika ada.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Jatah Kuota Laundry Free (Kg/Bln)</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Isi 0 jika tidak ada fasilitas laundry gratis</v>
+        <v>5. Kolom bertanda bintang (*) adalah kolom esensial/wajib.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>6. Setelah selesai diisi, kirim kembali file ini atau bagikan link Google Sheets ke WhatsApp: +6282114242634</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="35.83203125" customWidth="1"/>
+    <col min="2" max="2" width="45.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>No Kamar*</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Lantai*</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Tipe Kamar*</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Harga Sewa / Bulan (Rp)*</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Status Saat Ini (AVAILABLE/OCCUPIED/MAINTENANCE)*</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Ukuran Kamar</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Fasilitas Kamar (Pisahkan Koma)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Kapasitas (Orang)</v>
+        <v>=== KOSANKU PRO - DATA PROPERTI &amp; REKENING PENCAIRAN ===</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>MED-101</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Deluxe Doctor Suite</v>
-      </c>
-      <c r="D2">
-        <v>2200000</v>
-      </c>
-      <c r="E2" t="str">
-        <v>AVAILABLE</v>
-      </c>
-      <c r="F2" t="str">
-        <v>4 x 5 m (20 m2)</v>
-      </c>
-      <c r="G2" t="str">
-        <v>AC Daikin 1PK, Meja Kerja, KM Dalam Water Heater, Smart Key</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>Konsultasi &amp; Bantuan Setup WhatsApp: +6282114242634 (https://wa.me/6282114242634)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>MED-102</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Deluxe Doctor Suite</v>
-      </c>
-      <c r="D3">
-        <v>2200000</v>
-      </c>
-      <c r="E3" t="str">
-        <v>OCCUPIED</v>
-      </c>
-      <c r="F3" t="str">
-        <v>4 x 5 m (20 m2)</v>
-      </c>
-      <c r="G3" t="str">
-        <v>AC Daikin 1PK, Meja Kerja, KM Dalam Water Heater, Smart Key</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>MED-201</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
+        <v>PARAMETER / FIELD PENGATURAN*</v>
+      </c>
+      <c r="B4" t="str">
+        <v>ISIAN DATA OWNER</v>
       </c>
       <c r="C4" t="str">
-        <v>VIP Koas Balcony</v>
-      </c>
-      <c r="D4">
-        <v>2500000</v>
-      </c>
-      <c r="E4" t="str">
-        <v>AVAILABLE</v>
-      </c>
-      <c r="F4" t="str">
-        <v>5 x 5 m (25 m2)</v>
-      </c>
-      <c r="G4" t="str">
-        <v>AC Inverter, Smart TV 43 Inch, Balkon Private, Kulkas Mini, KM Dalam</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
+        <v>PETUNJUK PENGISIAN</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>MED-202</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
+        <v>Nama Properti / Kosan*</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>VIP Koas Balcony</v>
-      </c>
-      <c r="D5">
-        <v>2500000</v>
-      </c>
-      <c r="E5" t="str">
-        <v>OCCUPIED</v>
-      </c>
-      <c r="F5" t="str">
-        <v>5 x 5 m (25 m2)</v>
-      </c>
-      <c r="G5" t="str">
-        <v>AC Inverter, Smart TV 43 Inch, Balkon Private, Kulkas Mini, KM Dalam</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>Contoh: Kosan Asri Residence Bandung</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>MED-301</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
+        <v>Tagline / Slogan Kosan</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
       </c>
       <c r="C6" t="str">
-        <v>Standard Medico Room</v>
-      </c>
-      <c r="D6">
-        <v>1800000</v>
-      </c>
-      <c r="E6" t="str">
-        <v>AVAILABLE</v>
-      </c>
-      <c r="F6" t="str">
-        <v>3.5 x 4.5 m (16 m2)</v>
-      </c>
-      <c r="G6" t="str">
-        <v>AC Inverter, WiFi 100Mbps, Kasur Springbed, Lemari 2 Pintu</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
+        <v>Contoh: Hunian Nyaman &amp; Tenang Dekat Kampus</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>MED-302</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
+        <v>Alamat Lengkap Properti*</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
       </c>
       <c r="C7" t="str">
-        <v>Standard Medico Room</v>
-      </c>
-      <c r="D7">
-        <v>1800000</v>
-      </c>
-      <c r="E7" t="str">
-        <v>AVAILABLE</v>
-      </c>
-      <c r="F7" t="str">
-        <v>3.5 x 4.5 m (16 m2)</v>
-      </c>
-      <c r="G7" t="str">
-        <v>AC Inverter, WiFi 100Mbps, Kasur Springbed, Lemari 2 Pintu</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
+        <v>Contoh: Jl. Anggrek No. 12, RT 02/05, Kel. Sukajadi</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Kota / Wilayah*</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v>Contoh: Bandung / Jakarta Selatan</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>No. WhatsApp Resmi Kosan*</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v>No WA pengelola/admin untuk notifikasi tagihan &amp; komplain</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Email Resmi Pengelola</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>Email operasional kos (opsional)</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Link Google Maps</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>Link titik maps lokasi kos (opsional)</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Nama Bank Rekening Pencairan*</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>Contoh: BCA / Mandiri / BRI / BNI</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Nomor Rekening Bank*</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>Nomor rekening penampung uang sewa masuk</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Nama Pemilik Rekening (Holder)*</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v>Nama yang tertera di buku tabungan / rekening</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Batas Tanggal Jatuh Tempo Tagihan</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Tanggal 1 s/d 5 setiap bulan</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Default tanggal penagihan invoice otomatis</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Jatah Kuota Laundry Free (Kg/Bln)</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Isi 0 jika tidak ada kuota laundry gratis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:H14"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="45.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>No Kamar*</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Nama Lengkap Penghuni*</v>
-      </c>
-      <c r="C1" t="str">
-        <v>No WhatsApp*</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Email*</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Tanggal Masuk (DD/MM/YYYY)*</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Periode Sewa (Bulanan/3 Bulan/Tahunan)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Deposit Masuk (Rp)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>No KTP / NIK</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Instansi / Profesi</v>
+        <v>=== KOSANKU PRO - DAFTAR UNIT KAMAR ===</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>MED-102</v>
-      </c>
-      <c r="B2" t="str">
-        <v>dr. Rizky Pratama, Sp.A</v>
-      </c>
-      <c r="C2" t="str">
-        <v>081388776655</v>
-      </c>
-      <c r="D2" t="str">
-        <v>rizky.pratama@gmail.com</v>
-      </c>
-      <c r="E2" t="str">
-        <v>01/02/2026</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Bulanan</v>
-      </c>
-      <c r="G2">
-        <v>500000</v>
-      </c>
-      <c r="H2" t="str">
-        <v>3171012345670001</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Dokter Spesialis Anak RSHS</v>
+        <v>Konsultasi &amp; Bantuan Setup WhatsApp: +6282114242634 (https://wa.me/6282114242634)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>MED-202</v>
-      </c>
-      <c r="B3" t="str">
-        <v>drg. Anisa Putri</v>
-      </c>
-      <c r="C3" t="str">
-        <v>081299001122</v>
-      </c>
-      <c r="D3" t="str">
-        <v>anisa.putri@gmail.com</v>
-      </c>
-      <c r="E3" t="str">
-        <v>15/01/2026</v>
-      </c>
-      <c r="F3" t="str">
-        <v>3 Bulan</v>
-      </c>
-      <c r="G3">
-        <v>1000000</v>
-      </c>
-      <c r="H3" t="str">
-        <v>3273012345670002</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Koas Gigi FKG Unpad</v>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>No Kamar*</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Lantai*</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Tipe Kamar*</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Harga Sewa / Bulan (Rp)*</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Status Saat Ini (Kosong / Terisi / Renovasi)*</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Ukuran Kamar</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Fasilitas Kamar (Pisahkan Koma)</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Kapasitas (Orang)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:I9"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Kategori</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Nama Item Checklist</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Kondisi Standar Serah Terima</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Keterangan</v>
+        <v>=== KOSANKU PRO - DATA PENGHUNI AKTIF SAAT INI ===</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CHK-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>KUNCI</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Kunci Fisik &amp; Kartu Akses RFID</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Lengkap &amp; Berfungsi</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2 Kunci fisik + 1 Card Key RFID</v>
+        <v>Konsultasi &amp; Bantuan Setup WhatsApp: +6282114242634 (https://wa.me/6282114242634)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CHK-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>ELEKTRONIK</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Remote AC Original &amp; AC Berfungsi Dingin</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Menyala &amp; Dingin Normal</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Daikin / Panasonic</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CHK-03</v>
+        <v>No Kamar*</v>
       </c>
       <c r="B4" t="str">
-        <v>FURNITUR</v>
+        <v>Nama Lengkap Penghuni*</v>
       </c>
       <c r="C4" t="str">
-        <v>Kasur Springbed, Bantal &amp; Sprei Bersih</v>
+        <v>No WhatsApp Aktif*</v>
       </c>
       <c r="D4" t="str">
-        <v>Busa utuh &amp; Sprei Baru</v>
+        <v>Email*</v>
       </c>
       <c r="E4" t="str">
-        <v>Ukuran sesuai tipe kamar</v>
+        <v>Tanggal Masuk (DD/MM/YYYY)*</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Periode Sewa (Bulanan / 3 Bulan / Tahunan)</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Deposit Masuk (Rp)</v>
+      </c>
+      <c r="H4" t="str">
+        <v>No KTP / NIK</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Pekerjaan / Instansi</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CHK-04</v>
+        <v/>
       </c>
       <c r="B5" t="str">
-        <v>FURNITUR</v>
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>Lemari Pakaian, Meja Belajar &amp; Kursi</v>
+        <v/>
       </c>
       <c r="D5" t="str">
-        <v>Mulus tanpa retak / patah</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>Kunci lemari tersedia</v>
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CHK-05</v>
+        <v/>
       </c>
       <c r="B6" t="str">
-        <v>SANITASI</v>
+        <v/>
       </c>
       <c r="C6" t="str">
-        <v>Kran Wastafel, Shower &amp; Water Heater</v>
+        <v/>
       </c>
       <c r="D6" t="str">
-        <v>Air deras &amp; Pemanas menyala</v>
+        <v/>
       </c>
       <c r="E6" t="str">
-        <v>Bebas rembes</v>
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CHK-06</v>
+        <v/>
       </c>
       <c r="B7" t="str">
-        <v>DINDING_LANTAI</v>
+        <v/>
       </c>
       <c r="C7" t="str">
-        <v>Cat Dinding &amp; Kebersihan Lantai</v>
+        <v/>
       </c>
       <c r="D7" t="str">
-        <v>Bersih rapi tanpa coretan</v>
+        <v/>
       </c>
       <c r="E7" t="str">
-        <v>Lantai dipel wangi</v>
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
+  <cols>
+    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Tipe (KARYAWAN/VENDOR)*</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Nama Lengkap / Nama Usaha*</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Kontak No WhatsApp*</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Email / Bidang Layanan*</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Gaji / Biaya Langganan (Rp)</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Alamat / Catatan</v>
+        <v>=== KOSANKU PRO - DATA KARYAWAN &amp; VENDOR MITRA ===</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>KARYAWAN</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Bambang Prasetyo</v>
-      </c>
-      <c r="C2" t="str">
-        <v>081355443322</v>
-      </c>
-      <c r="D2" t="str">
-        <v>staf.maintenance@kosanku.pro</v>
-      </c>
-      <c r="E2">
-        <v>3500000</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Teknisi Listrik, Pompa &amp; AC</v>
+        <v>Konsultasi &amp; Bantuan Setup WhatsApp: +6282114242634 (https://wa.me/6282114242634)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>KARYAWAN</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Siti Aminah</v>
-      </c>
-      <c r="C3" t="str">
-        <v>081244332211</v>
-      </c>
-      <c r="D3" t="str">
-        <v>admin.operasional@kosanku.pro</v>
-      </c>
-      <c r="E3">
-        <v>3200000</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Pengawas Kebersihan &amp; Komplain</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>VENDOR</v>
+        <v>Tipe (KARYAWAN / VENDOR)*</v>
       </c>
       <c r="B4" t="str">
-        <v>Depot Air &amp; Gas Suci</v>
+        <v>Nama Lengkap / Nama Usaha Toko*</v>
       </c>
       <c r="C4" t="str">
-        <v>081299887711</v>
+        <v>Kontak No WhatsApp*</v>
       </c>
       <c r="D4" t="str">
-        <v>Refill Aqua 19L &amp; Gas LPG 3kg</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
+        <v>Posisi / Bidang Layanan*</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Gaji / Biaya Langganan (Rp)</v>
       </c>
       <c r="F4" t="str">
-        <v>Jl. Pemuda No. 12 (Delivery 15 menit)</v>
+        <v>Alamat / Catatan Tambahan</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>VENDOR</v>
+        <v/>
       </c>
       <c r="B5" t="str">
-        <v>Laundry Express Pasteur</v>
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>081344556677</v>
+        <v/>
       </c>
       <c r="D5" t="str">
-        <v>Jasa Laundry Kiloan Tenant</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>Depan Gapura Kosan (Rp 6.000/kg)</v>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
   </ignoredErrors>
 </worksheet>
 </file>